--- a/fixtures/xlsx/freeze-pane/input.xlsx
+++ b/fixtures/xlsx/freeze-pane/input.xlsx
@@ -10,22 +10,22 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
-    <t>Row 4</t>
+    <t>Row 5</t>
+  </si>
+  <si>
+    <t>Value</t>
   </si>
   <si>
     <t>Name</t>
   </si>
   <si>
+    <t>Row 3</t>
+  </si>
+  <si>
     <t>Row 2</t>
   </si>
   <si>
-    <t>Value</t>
-  </si>
-  <si>
-    <t>Row 3</t>
-  </si>
-  <si>
-    <t>Row 5</t>
+    <t>Row 4</t>
   </si>
 </sst>
 </file>
@@ -35,15 +35,15 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B2">
         <v>2</v>
@@ -51,7 +51,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B3">
         <v>3</v>
@@ -59,7 +59,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="B4">
         <v>4</v>
@@ -67,7 +67,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="B5">
         <v>5</v>

--- a/fixtures/xlsx/freeze-pane/input.xlsx
+++ b/fixtures/xlsx/freeze-pane/input.xlsx
@@ -10,22 +10,22 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
-    <t>Row 5</t>
+    <t>Row 3</t>
   </si>
   <si>
     <t>Value</t>
-  </si>
-  <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>Row 3</t>
   </si>
   <si>
     <t>Row 2</t>
   </si>
   <si>
     <t>Row 4</t>
+  </si>
+  <si>
+    <t>Row 5</t>
+  </si>
+  <si>
+    <t>Name</t>
   </si>
 </sst>
 </file>
@@ -35,7 +35,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
@@ -43,7 +43,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B2">
         <v>2</v>
@@ -51,7 +51,7 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B3">
         <v>3</v>
@@ -59,7 +59,7 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B4">
         <v>4</v>
@@ -67,7 +67,7 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B5">
         <v>5</v>
